--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,24 +642,24 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站博兴路兰城路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±9分钟</t>
+          <t>07:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/8</t>
+          <t>2/19</t>
         </is>
       </c>
     </row>
@@ -761,19 +761,19 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>06:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>07:20采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/8</t>
+          <t>3/19</t>
         </is>
       </c>
     </row>
@@ -880,24 +880,24 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:36</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±9分钟</t>
+          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/8</t>
+          <t>1/19</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1332,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:13</t>
+          <t>09:25</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>164分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数152分钟估算，约±7分钟</t>
+          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/8</t>
+          <t>10/19</t>
         </is>
       </c>
     </row>
@@ -1451,19 +1451,19 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数164分钟估算，约±5分钟</t>
+          <t>07:12采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1507,32 +1507,1317 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>09:25</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>06:55</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>160分钟</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>160.0</t>
+        </is>
+      </c>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>8/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>164.0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>5/8</t>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>11/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>159分钟</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:25</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>159.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>7/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:41</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>5/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>171分钟</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>13/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -637,29 +637,29 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路北中路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±7分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -756,29 +756,29 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:26</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站迎春路金松路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/19</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1221,19 +1221,19 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 82分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1332,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>164分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站沪南路华夏西路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±13分钟</t>
+          <t>08:10采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>159.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/19</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -1451,24 +1451,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>182分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>07:12采样：该车到重点站川周公路康沈路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1527,12 +1527,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1570,19 +1570,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:25</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站博兴路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站浦建路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>161.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1689,24 +1689,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站川周公路康沈路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数138分钟，约±5分钟</t>
+          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -1808,19 +1808,19 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>160分钟</t>
+          <t>166分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>07:20采样：该车到重点站莱阳路东陆路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数141分钟，约±6分钟</t>
+          <t>08:10采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>160.0</t>
+          <t>166.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/19</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/19</t>
+          <t>11/27</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2268,24 +2268,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10:04</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数159分钟估算，约±8分钟</t>
+          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2344,12 +2344,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>158.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/19</t>
+          <t>8/27</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2498,24 +2498,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数151分钟估算，约±6分钟</t>
+          <t>08:10采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/19</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -2617,19 +2617,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>176分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数171分钟估算，约±6分钟</t>
+          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>176.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/19</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2736,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+          <t>08:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2792,32 +2792,1071 @@
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>181分钟</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>08:01采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数170分钟，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>181.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>16/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>08:10采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>6/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>166分钟</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="Y24" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr">
-        <is>
-          <t>144.0</t>
-        </is>
-      </c>
-      <c r="AC20" s="2" t="inlineStr">
-        <is>
-          <t>4/19</t>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>11/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>145.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>145分钟</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:10</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>7/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC29"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,12 +642,12 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -761,12 +761,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -999,19 +999,19 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 48分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr"/>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1226,17 +1226,21 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>172分钟</t>
+          <t>171分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:10采样，终点ETA 82分钟</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,17 +1272,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1288,13 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>171.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>16/27</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±8分钟</t>
+          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1408,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>159.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1451,24 +1459,24 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>182分钟</t>
+          <t>179分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±10分钟</t>
+          <t>08:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1478,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1527,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>179.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>18/27</t>
         </is>
       </c>
     </row>
@@ -1570,19 +1578,19 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>161分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦建路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站浦建路锦绣路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1597,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1646,12 +1654,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>161.0</t>
+          <t>170.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>15/27</t>
         </is>
       </c>
     </row>
@@ -1689,19 +1697,19 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:59</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站沪南路高科西路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
+          <t>08:20采样：该车到重点站沪南路高科西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1716,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1765,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>175.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>17/27</t>
         </is>
       </c>
     </row>
@@ -1808,24 +1816,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站白桦路明月路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±6分钟</t>
+          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1835,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1884,12 +1892,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>162.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>10/27</t>
         </is>
       </c>
     </row>
@@ -1950,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2119,7 +2127,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>12/27</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2188,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2268,24 +2276,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路云山路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数105分钟，约±9分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2295,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2344,12 +2352,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>158.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/27</t>
+          <t>9/27</t>
         </is>
       </c>
     </row>
@@ -2498,19 +2506,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站金杨路金业路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站白桦路明月路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2525,7 +2533,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2574,12 +2582,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -2617,19 +2625,19 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>176分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数154分钟，约±6分钟</t>
+          <t>08:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2644,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2693,12 +2701,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>176.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>14/27</t>
         </is>
       </c>
     </row>
@@ -2736,24 +2744,24 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±7分钟</t>
+          <t>08:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2763,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2812,12 +2820,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>19/27</t>
         </is>
       </c>
     </row>
@@ -2974,19 +2982,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:10采样：该车到重点站浦东大道东波路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数136分钟，约±5分钟</t>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3001,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3050,12 +3058,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>7/27</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3209,14 +3217,14 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±5分钟</t>
+          <t>08:20采样：该车到重点站康丽路康恩路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数162分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3231,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3260,7 +3268,7 @@
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
@@ -3280,12 +3288,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/27</t>
+          <t>13/27</t>
         </is>
       </c>
     </row>
@@ -3323,22 +3331,26 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3346,7 +3358,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3370,17 +3382,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3390,13 +3402,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>5/27</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3737,7 +3753,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>6/27</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3818,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3851,12 +3867,131 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>7/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>144分钟</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>141.5</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AC37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,14 +446,14 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -880,19 +880,19 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>06:50采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>同车下一次反向发车09:20，减去该车自身同类时段历史终点停站中位数32分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -994,27 +994,31 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>09:08</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>158分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：08:20采样，终点ETA 48分钟</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1221,24 +1229,24 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>171分钟</t>
+          <t>174分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>171.0</t>
+          <t>174.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>16/27</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1343,29 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>09:24</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>158分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站锦绣路罗山路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数62分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1391,12 +1399,12 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
@@ -1406,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1459,26 +1467,22 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>179分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站锦绣路花木路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±8分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 36分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1510,12 +1514,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1535,12 +1539,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>179.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1577,29 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>170分钟</t>
+          <t>172分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站浦建路锦绣路 ETA 21分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1629,12 +1633,12 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
@@ -1644,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>170.0</t>
+          <t>172.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/27</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1701,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>175分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站沪南路高科西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±10分钟</t>
+          <t>09:10采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1777,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>167.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/27</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1816,24 +1820,24 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>162分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±7分钟</t>
+          <t>09:10采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1892,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/27</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1925,12 +1929,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq45，推进4站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1966,10 +1970,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1987,7 +2003,7 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
@@ -2008,7 +2024,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/27</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2238,7 +2254,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2276,24 +2292,24 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站白桦路明月路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±8分钟</t>
+          <t>09:10采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2303,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2352,12 +2368,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/27</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2434,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2468,7 +2484,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2506,19 +2522,19 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站白桦路明月路 ETA 19分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2533,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2582,12 +2598,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2625,24 +2641,24 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站康沈路秀康路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数126分钟，约±6分钟</t>
+          <t>09:10采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2652,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2701,12 +2717,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/27</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2749,19 +2765,19 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站金杨路金业路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±8分钟</t>
+          <t>09:01采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2771,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2820,12 +2836,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2863,24 +2879,24 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>181分钟</t>
+          <t>169分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>08:01采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数170分钟，约±9分钟</t>
+          <t>09:10采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2890,7 +2906,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2939,12 +2955,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>169.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/27</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2982,19 +2998,19 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -3009,7 +3025,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3058,12 +3074,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3140,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3174,7 +3190,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3212,19 +3228,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站康丽路康恩路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数162分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3239,7 +3255,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3288,12 +3304,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>155.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/27</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3331,19 +3347,19 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>08:20采样：该车到重点站莱阳路东陆路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数120分钟，约±5分钟</t>
+          <t>09:10采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
@@ -3358,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3407,12 +3423,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3450,22 +3466,26 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3473,7 +3493,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3497,17 +3517,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3517,13 +3537,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3561,22 +3585,26 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>09:10采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3584,7 +3612,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3608,17 +3636,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3628,13 +3656,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3672,19 +3704,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+          <t>09:10采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3699,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3728,7 +3760,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3748,12 +3780,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/27</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3791,19 +3823,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数145分钟估算，约±5分钟</t>
+          <t>09:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3818,7 +3850,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3847,7 +3879,7 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3867,12 +3899,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>147.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/27</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3922,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3910,24 +3942,24 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数144分钟估算，约±6分钟</t>
+          <t>09:10采样：该车到重点站关岳路康达路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3937,7 +3969,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3951,7 +3983,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3966,32 +3998,841 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>136分钟</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y30" s="2" t="inlineStr">
+      <c r="Y31" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z30" s="2" t="inlineStr">
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
+      <c r="AA31" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB30" s="2" t="inlineStr">
-        <is>
-          <t>141.5</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr">
-        <is>
-          <t>4/27</t>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>147.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A72305D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>08:40</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:24</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>174.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>172.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>09:35</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>174分钟</t>
+          <t>173分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1462,27 +1462,31 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>170分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：09:10采样，终点ETA 36分钟</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1514,12 +1518,12 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
@@ -1529,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>150.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1696,29 +1700,29 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>167分钟</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金杨路金口路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1752,12 +1756,12 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
@@ -1767,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>167.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1815,24 +1819,24 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站康沈路秀沿路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数29分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,12 +1875,12 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
@@ -1886,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1934,7 +1938,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq45，推进4站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq41推进至seq60，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2062,24 +2066,24 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>166分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数166分钟估算，约±9分钟</t>
+          <t>同车下一次反向发车10:19，减去该车自身同类时段历史终点停站中位数6分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -2089,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2113,12 +2117,12 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
@@ -2128,22 +2132,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>166.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2175,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq37推进至seq59，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2212,10 +2216,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置浦建路锦绣路 ETA 10分钟参与校验</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2233,7 +2253,7 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
@@ -2287,29 +2307,29 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>09:52</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2319,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2343,12 +2363,12 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
@@ -2358,22 +2378,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2406,27 +2426,31 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>165分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2434,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2458,33 +2482,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2517,24 +2545,24 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>10:05</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
@@ -2549,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2573,12 +2601,12 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
@@ -2588,17 +2616,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2636,12 +2664,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2653,12 +2681,12 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2668,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,12 +2720,12 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
@@ -2707,22 +2735,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2755,24 +2783,24 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>09:01采样：该车到重点站浦建路锦绣路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2787,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,12 +2839,12 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
@@ -2826,22 +2854,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2891,14 +2919,10 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2906,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2930,12 +2954,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2960,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2998,26 +3022,22 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 8分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3025,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3054,7 +3074,7 @@
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3074,12 +3094,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3160,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3228,19 +3248,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:53</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路华夏西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站五莲路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3255,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3304,12 +3324,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3347,26 +3367,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3374,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,12 +3414,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3423,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3466,19 +3482,19 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数84分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3493,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3542,12 +3558,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3585,19 +3601,19 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数110分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3612,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3661,12 +3677,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3704,19 +3720,19 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站康沈路秀康路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -3731,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3780,12 +3796,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3823,19 +3839,19 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站莱阳路东陆路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数128分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3850,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3899,12 +3915,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3942,19 +3958,19 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>09:10采样：该车到重点站关岳路康达路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数127分钟，约±5分钟</t>
+          <t>10:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
@@ -3969,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4018,12 +4034,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4061,24 +4077,24 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数136分钟估算，约±9分钟</t>
+          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -4088,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4117,7 +4133,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4137,12 +4153,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>147.5</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4180,24 +4196,24 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+          <t>10:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -4207,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4236,7 +4252,7 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4256,12 +4272,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4521,24 +4537,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±12分钟</t>
+          <t>10:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4548,7 +4564,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,12 +4588,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4597,12 +4613,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4679,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4712,12 +4728,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>174.0</t>
+          <t>173.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -4725,24 +4741,24 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4755,30 +4771,34 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>10:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4792,47 +4812,1110 @@
       <c r="T37" s="2" t="inlineStr"/>
       <c r="U37" s="2" t="inlineStr">
         <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>150.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="V37" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W37" s="2" t="inlineStr">
+      <c r="W38" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X37" s="2" t="inlineStr">
+      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y37" s="2" t="inlineStr">
+      <c r="Y38" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA37" s="2" t="inlineStr">
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>172.0</t>
         </is>
       </c>
-      <c r="AC37" s="2" t="inlineStr">
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站博兴路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>131分钟</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>10:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
         <is>
           <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>12:37</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>165.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>136.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>173分钟</t>
+          <t>175分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2902,27 +2902,31 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>169分钟</t>
+          <t>167分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2930,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2954,12 +2958,12 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
@@ -2969,22 +2973,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>169.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3017,27 +3021,31 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 8分钟</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3069,12 +3077,12 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
@@ -3084,22 +3092,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3132,27 +3140,31 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3160,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3184,17 +3196,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3204,13 +3216,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>155.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3248,19 +3264,19 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:46</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站五莲路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数23分钟，约±5分钟</t>
+          <t>10:31采样：该车到重点站东波路莱阳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数18分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
@@ -3275,7 +3291,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,22 +3330,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>149.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3362,27 +3378,31 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：10:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3390,7 +3410,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3414,12 +3434,12 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
@@ -3439,12 +3459,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3477,24 +3497,24 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数30分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3509,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,12 +3553,12 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
@@ -3558,12 +3578,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3596,24 +3616,24 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数41分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3628,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,12 +3672,12 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
@@ -3667,22 +3687,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3720,26 +3740,22 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数28分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：10:50采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -3747,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3776,7 +3792,7 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
@@ -3786,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3834,24 +3850,24 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3866,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,12 +3906,12 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
@@ -3915,12 +3931,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3958,26 +3974,22 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:08</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数46分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:01采样，终点ETA 7分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3985,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4014,7 +4026,7 @@
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
@@ -4034,7 +4046,7 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4077,26 +4089,22 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站浦建路锦绣路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4104,7 +4112,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4133,7 +4141,7 @@
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
@@ -4143,22 +4151,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4191,24 +4199,24 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -4223,7 +4231,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4247,12 +4255,12 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
@@ -4262,22 +4270,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4305,12 +4313,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4338,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4346,10 +4354,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q33" s="2" t="inlineStr"/>
-      <c r="R33" s="2" t="inlineStr"/>
-      <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
           <t>09:24</t>
@@ -4367,7 +4391,7 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
@@ -4537,26 +4561,22 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数70分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 26分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4564,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4588,12 +4608,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4613,12 +4633,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4699,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4733,7 +4753,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4771,24 +4791,24 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±7分钟</t>
+          <t>11:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4798,7 +4818,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4847,12 +4867,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>150.5</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4933,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4967,7 +4987,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5005,24 +5025,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站博兴路兰城路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+          <t>11:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5032,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5081,12 +5101,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5124,19 +5144,19 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站关岳路康达路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数118分钟，约±8分钟</t>
+          <t>11:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -5151,7 +5171,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5200,12 +5220,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5243,19 +5263,19 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>10:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数121分钟，约±5分钟</t>
+          <t>10:31采样：该车到重点站莱阳路东陆路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -5270,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5319,7 +5339,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5362,7 +5382,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
@@ -5374,12 +5394,12 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+          <t>11:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5389,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5418,7 +5438,7 @@
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5443,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5524,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5558,7 +5578,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5596,24 +5616,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5623,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5652,7 +5672,7 @@
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5677,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5715,24 +5735,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5742,7 +5762,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5766,12 +5786,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5791,12 +5811,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5834,24 +5854,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>11:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5861,7 +5881,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5890,32 +5910,861 @@
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>132.5</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>15/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>11:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>149.5</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>124分钟</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y46" s="2" t="inlineStr">
+      <c r="Y49" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>133.0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>3/28</t>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>139分钟</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>143.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,18 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2278,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2388,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2502,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2616,22 +2620,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2745,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2864,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3102,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>25/29</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3340,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -3648,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3692,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3812,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4161,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -4231,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4280,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4322,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq58，推进30站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -4346,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4416,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4527,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>—/29</t>
         </is>
       </c>
     </row>
@@ -4556,27 +4560,31 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：11:11采样，终点ETA 26分钟</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4584,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4608,12 +4616,12 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
@@ -4633,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4671,27 +4679,31 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4699,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4735,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4743,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>173.0</t>
+          <t>151.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4798,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4796,19 +4808,19 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4818,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,12 +4854,12 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
@@ -4857,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>145.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>18/29</t>
         </is>
       </c>
     </row>
@@ -4905,27 +4917,31 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4933,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,37 +4973,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>172.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -5020,29 +5036,29 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路御桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数36分钟，约±6分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5052,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,12 +5092,12 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
@@ -5101,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5139,12 +5155,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -5156,12 +5172,12 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5171,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5195,12 +5211,12 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
@@ -5210,22 +5226,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5344,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/29</t>
         </is>
       </c>
     </row>
@@ -5377,29 +5393,29 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站锦绣路花木路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5409,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5433,12 +5449,12 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
@@ -5458,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>135.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5496,27 +5512,31 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5524,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5548,17 +5568,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5568,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>165.0</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -5616,26 +5636,22 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站白桦路明月路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 32分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5643,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,12 +5683,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5692,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>24/29</t>
         </is>
       </c>
     </row>
@@ -5735,26 +5751,22 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5762,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5791,7 +5803,7 @@
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5801,22 +5813,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5854,24 +5866,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站康沈路秀康路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±6分钟</t>
+          <t>12:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5881,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5930,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5997,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数101分钟，约±5分钟</t>
+          <t>12:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6000,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6054,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6092,24 +6104,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±8分钟</t>
+          <t>12:21采样：该车到重点站沪南路北中路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6119,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6168,12 +6180,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>149.5</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6211,24 +6223,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数124分钟估算，约±7分钟</t>
+          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6238,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6267,7 +6279,7 @@
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6287,12 +6299,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6342,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数139分钟估算，约±14分钟</t>
+          <t>12:21采样：该车到重点站丁香路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6357,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6386,7 +6398,7 @@
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6406,12 +6418,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -6449,22 +6461,26 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6472,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6496,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6516,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -6564,24 +6580,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±9分钟</t>
+          <t>12:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6591,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6620,7 +6636,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6640,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6683,19 +6699,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±14分钟</t>
+          <t>12:21采样：该车到重点站沪南路高科西路 ETA 49分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6739,32 +6755,734 @@
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>16/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>126分钟</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y53" s="2" t="inlineStr">
+      <c r="Y54" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z53" s="2" t="inlineStr">
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
+      <c r="AA54" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB53" s="2" t="inlineStr">
-        <is>
-          <t>143.7</t>
-        </is>
-      </c>
-      <c r="AC53" s="2" t="inlineStr">
-        <is>
-          <t>11/28</t>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>—/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>145.7</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>18/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>128分钟</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>139.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>9/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5398,24 +5398,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>135.5</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5631,27 +5631,31 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -5659,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5687,12 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
@@ -5708,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>153.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5746,27 +5750,31 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：12:21采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5774,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5798,12 +5806,12 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
@@ -5823,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5866,19 +5874,19 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站金杨路金口路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数39分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站长岛路张杨北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5893,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5997,12 +6005,12 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±7分钟</t>
+          <t>12:31采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -6012,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -6104,19 +6112,19 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:43</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路北中路 ETA 23分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
+          <t>12:31采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -6131,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6180,12 +6188,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6223,24 +6231,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站锦绣路花木路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±9分钟</t>
+          <t>12:31采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6250,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6299,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6354,7 +6362,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站丁香路锦绣路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
+          <t>12:31采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -6369,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6461,19 +6469,19 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>12:31采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -6488,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>144.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6588,19 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数108分钟，约±8分钟</t>
+          <t>12:31采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
@@ -6607,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6664,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6699,19 +6707,19 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:21采样：该车到重点站沪南路高科西路 ETA 49分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
+          <t>12:31采样：该车到重点站沪南路高科西路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
@@ -6726,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,12 +6783,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6826,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±7分钟</t>
+          <t>12:31采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,12 +6877,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6894,12 +6902,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7075,7 +7083,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7137,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>18/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7202,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7313,7 +7321,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7428,7 +7436,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,12 +7485,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,22 +3096,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,17 +3453,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3691,22 +3691,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>12/29</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4155,22 +4155,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>146.5</t>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>20/29</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5755,24 +5755,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -5869,24 +5869,24 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站长岛路张杨北路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数32分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,12 +5925,12 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -5998,21 +5998,17 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站沪南路御桥路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数34分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：12:50采样，终点ETA 15分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6020,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6049,7 +6045,7 @@
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
@@ -6059,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -6107,29 +6103,29 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±7分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6139,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6163,12 +6159,12 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
@@ -6188,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>137.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -6226,29 +6222,29 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站锦绣路罗山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数56分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6258,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6282,12 +6278,12 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
@@ -6297,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6345,29 +6341,29 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数88分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6377,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,12 +6397,12 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
@@ -6426,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -6469,26 +6465,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:07</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站沪南路华夏西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 57分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6496,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6520,37 +6512,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -6588,24 +6580,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±8分钟</t>
+          <t>13:21采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6615,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6664,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>131.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>3/29</t>
         </is>
       </c>
     </row>
@@ -6707,26 +6699,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站沪南路高科西路 ETA 37分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±14分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 61分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6734,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6758,37 +6746,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6826,24 +6814,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>12:31采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数123分钟，约±11分钟</t>
+          <t>13:21采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6853,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6877,7 +6865,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
@@ -6902,12 +6890,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7056,24 +7044,24 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±5分钟</t>
+          <t>13:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7083,7 +7071,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7112,7 +7100,7 @@
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7132,12 +7120,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>145.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -7175,24 +7163,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数128分钟估算，约±10分钟</t>
+          <t>13:21采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7202,7 +7190,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7226,12 +7214,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7251,12 +7239,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7294,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±6分钟</t>
+          <t>13:21采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7321,7 +7309,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7350,7 +7338,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7375,7 +7363,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -7413,22 +7401,26 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>13:21采样：该车到重点站莱阳路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7436,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7460,37 +7452,739 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X59" s="2" t="inlineStr">
+      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y59" s="2" t="inlineStr">
+      <c r="Y60" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z59" s="2" t="inlineStr">
+      <c r="Z60" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
+      <c r="AA60" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB59" s="2" t="inlineStr">
-        <is>
-          <t>138.0</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>8/29</t>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>146.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>20/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>138.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57051D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>140分钟</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>19/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>21/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>16:43</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>143.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>15/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>140.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>19/29</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,17 +3696,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,17 +3925,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>5/29</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4160,17 +4160,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,22 +4631,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>138.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>13/29</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4869,22 +4869,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>8/29</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>7/29</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>11/29</t>
         </is>
       </c>
     </row>
@@ -6227,24 +6227,24 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>2/29</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
@@ -6470,17 +6470,21 @@
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:10采样，终点ETA 57分钟</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6488,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6512,17 +6516,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6532,17 +6536,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -6580,26 +6584,22 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站沪南路御桥路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：13:50采样，终点ETA 16分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.3</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -6704,17 +6704,21 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：13:21采样，终点ETA 61分钟</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6766,17 +6770,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>10/29</t>
         </is>
       </c>
     </row>
@@ -6809,29 +6813,29 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站丁香路锦绣路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±8分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6841,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6865,12 +6869,12 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
@@ -6890,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>15/29</t>
         </is>
       </c>
     </row>
@@ -6923,12 +6927,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6956,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6964,10 +6968,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q55" s="2" t="inlineStr"/>
-      <c r="R55" s="2" t="inlineStr"/>
-      <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 7分钟参与校验</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>12:30</t>
@@ -6985,7 +7005,7 @@
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
@@ -7044,26 +7064,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站沪南路高科西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±6分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：14:10采样，终点ETA 39分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7071,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7095,12 +7111,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7110,22 +7126,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>14/29</t>
         </is>
       </c>
     </row>
@@ -7163,24 +7179,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数95分钟，约±11分钟</t>
+          <t>14:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7190,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7214,7 +7230,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
@@ -7239,12 +7255,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>9/29</t>
         </is>
       </c>
     </row>
@@ -7282,19 +7298,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:08</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站康沈路秀康路 ETA 10分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±6分钟</t>
+          <t>同车下一次反向发车15:25，减去该车自身同类时段历史终点停站中位数17分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7309,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7338,7 +7354,7 @@
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>同车反向发车反推</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7348,22 +7364,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/29</t>
         </is>
       </c>
     </row>
@@ -7401,19 +7417,19 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>13:21采样：该车到重点站莱阳路东陆路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>14:20采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
@@ -7428,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7477,12 +7493,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>4/29</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7597,7 +7613,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>20/29</t>
+          <t>21/29</t>
         </is>
       </c>
     </row>
@@ -7635,22 +7651,26 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>14:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7658,7 +7678,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,17 +7702,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7702,17 +7722,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>6/29</t>
         </is>
       </c>
     </row>
@@ -7750,19 +7770,19 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数140分钟估算，约±8分钟</t>
+          <t>14:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
@@ -7777,7 +7797,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7806,7 +7826,7 @@
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7826,7 +7846,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7892,7 +7912,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7956,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>16/29</t>
         </is>
       </c>
     </row>
@@ -7984,7 +8004,7 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -7996,12 +8016,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±15分钟</t>
+          <t>14:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8011,7 +8031,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8040,7 +8060,7 @@
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8065,7 +8085,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>17/29</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8150,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8194,493 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>137.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>132分钟</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>140.3</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>11/29</t>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>12/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>138.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>13/29</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>17:34</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>1/29</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC69"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2754,7 +2754,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>155.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/29</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/29</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4416,7 +4416,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>146.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/29</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/29</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/29</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/29</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/29</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/29</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -6818,24 +6818,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/29</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6932,7 +6932,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/29</t>
+          <t>—/30</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7059,7 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7069,17 +7069,21 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：14:10采样，终点ETA 39分钟</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7087,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7111,12 +7115,12 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
@@ -7141,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7174,29 +7178,29 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站沪南路御桥路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数37分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7230,12 +7234,12 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
@@ -7255,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/29</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7293,29 +7297,29 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:08</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>同车下一次反向发车15:25，减去该车自身同类时段历史终点停站中位数17分钟，约±6分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7325,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,12 +7353,12 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>同车反向发车反推</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
@@ -7374,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7412,29 +7416,29 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站浦建路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数61分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7444,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,12 +7472,12 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
@@ -7493,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/29</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7531,27 +7535,31 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7559,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,17 +7591,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7603,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>146.5</t>
+          <t>143.3</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/29</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7646,29 +7654,29 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7678,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,12 +7710,12 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
@@ -7727,12 +7735,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/29</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7790,12 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站康沈路秀康路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±8分钟</t>
+          <t>15:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7797,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7851,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>19/29</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7912,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7966,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/29</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -8004,24 +8012,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>14:20采样：该车到重点站关岳路康达路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数134分钟，约±14分钟</t>
+          <t>15:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8031,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,7 +8063,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
@@ -8080,12 +8088,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/29</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8123,7 +8131,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -8135,7 +8143,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>15:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
@@ -8150,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8179,7 +8187,7 @@
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8204,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/29</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8242,24 +8250,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:57</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数132分钟估算，约±10分钟</t>
+          <t>15:21采样：该车到重点站沪南路高科西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8269,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,12 +8301,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8318,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>139.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>12/29</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8361,24 +8369,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±8分钟</t>
+          <t>15:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8388,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8417,7 +8425,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8442,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/29</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8480,24 +8488,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±12分钟</t>
+          <t>15:21采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±15分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8507,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8536,7 +8544,7 @@
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8556,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>138.7</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/29</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8626,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8675,12 +8683,591 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>1/29</t>
+          <t>5/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±13分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>140.7</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>18:22</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>157分钟</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>156.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>18:16</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>135分钟</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>146.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>—/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,14 +1295,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2987,7 +2987,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,17 +3334,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3453,22 +3453,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>134.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,22 +4274,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,14 +4750,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>151.5</t>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>149.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>153.5</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,17 +6174,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>137.5</t>
+          <t>136.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,22 +6412,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6536,12 +6536,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>129.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7552,12 +7552,12 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7659,24 +7659,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>134.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7773,29 +7773,29 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站云山路碧云路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数52分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,12 +7829,12 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7892,27 +7892,31 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7920,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7944,17 +7948,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7964,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8007,29 +8011,29 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站迎春路金松路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±9分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,12 +8067,12 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
@@ -8078,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8126,29 +8130,29 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8158,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,12 +8186,12 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
@@ -8207,12 +8211,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8250,26 +8254,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站沪南路高科西路 ETA 17分钟；叠加该车自身同类时段从该站到终点历史中位数83分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 43分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>139.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8369,24 +8369,24 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数104分钟，约±7分钟</t>
+          <t>16:20采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -8488,24 +8488,24 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:26</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>15:21采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±15分钟</t>
+          <t>16:20采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>140.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -8619,7 +8619,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8663,7 +8663,7 @@
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8837,24 +8837,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±13分钟</t>
+          <t>16:20采样：该车到重点站沪南路高科西路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±14分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>140.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8956,19 +8956,19 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数157分钟估算，约±5分钟</t>
+          <t>16:20采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9012,7 +9012,7 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>154.5</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9045,24 +9045,24 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>16:01</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -9075,34 +9075,34 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数135分钟估算，约±8分钟</t>
+          <t>16:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9141,22 +9141,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>146.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A15330A</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9174,7 +9174,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9194,30 +9194,34 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>16:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9231,43 +9235,983 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>149.3</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>23/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>16:08</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA75" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr"/>
-      <c r="AC74" s="2" t="inlineStr">
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr">
         <is>
           <t>—/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>137分钟</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站川周公路康沈路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±15分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>16:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±8分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>134.3</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>134分钟</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>136.3</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>151.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>138分钟</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>131.7</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>19:09</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>129分钟</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±12分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>129.2</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>1/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>140.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>15/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,7 +3225,7 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3458,17 +3458,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3652,7 +3652,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -4116,7 +4116,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4165,7 +4165,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,12 +4879,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -7897,24 +7897,24 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8016,24 +8016,24 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8087,17 +8087,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>141.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8135,24 +8135,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8162,7 +8162,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -8259,17 +8259,21 @@
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：16:20采样，终点ETA 43分钟</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8277,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,12 +8305,12 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
@@ -8316,7 +8320,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8326,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8369,26 +8373,22 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:34</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路北中路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 13分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8445,12 +8445,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>142.2</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -8483,29 +8483,29 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>17:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站迎春路金松路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数66分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>140.7</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8602,29 +8602,29 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站丁香路锦绣路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8634,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,12 +8658,12 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
@@ -8673,22 +8673,22 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -8716,12 +8716,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,10 +8757,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>物理seq27（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:35</t>
@@ -8778,7 +8794,7 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
@@ -8832,29 +8848,29 @@
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站沪南路高科西路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数82分钟，约±14分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8864,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8904,12 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
@@ -8913,12 +8929,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>140.3</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -8956,24 +8972,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数114分钟，约±5分钟</t>
+          <t>17:21采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±8分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8983,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9032,7 +9048,7 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>154.5</t>
+          <t>154.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9075,24 +9091,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>122分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站博兴路兰城路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数100分钟，约±10分钟</t>
+          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9102,7 +9118,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,7 +9142,7 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
@@ -9151,12 +9167,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -9194,24 +9210,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站康沈路秀康路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±8分钟</t>
+          <t>16:40采样：该车到重点站沪南路华夏西路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数98分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9221,7 +9237,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9270,12 +9286,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>149.3</t>
+          <t>148.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9352,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9424,24 +9440,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站川周公路康沈路 ETA 15分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±15分钟</t>
+          <t>17:21采样：该车到重点站锦绣路花木路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9451,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9500,12 +9516,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>152.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9559,7 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -9555,12 +9571,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>16:20采样：该车到重点站浦东大道东波路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数129分钟，约±8分钟</t>
+          <t>17:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9570,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,7 +9610,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
@@ -9624,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -9662,19 +9678,19 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>145分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数134分钟估算，约±5分钟</t>
+          <t>17:21采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9689,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9718,7 +9734,7 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9738,12 +9754,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>136.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -9781,22 +9797,26 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站丁香路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -9804,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9848,17 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
@@ -9848,17 +9868,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>151.5</t>
+          <t>152.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9896,24 +9916,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:03</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数138分钟估算，约±14分钟</t>
+          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9923,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9952,7 +9972,7 @@
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9972,7 +9992,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10015,19 +10035,19 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数129分钟估算，约±12分钟</t>
+          <t>17:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
@@ -10042,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10071,7 +10091,7 @@
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10091,7 +10111,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.2</t>
+          <t>129.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10134,22 +10154,26 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>17:21采样：该车到重点站金杨路金业路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10157,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10181,37 +10205,854 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>141.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>150分钟</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>143.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>19:56</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>156分钟</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>13/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X82" s="2" t="inlineStr">
+      <c r="X85" s="2" t="inlineStr">
         <is>
           <t>证据不足</t>
         </is>
       </c>
-      <c r="Y82" s="2" t="inlineStr">
+      <c r="Y85" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB82" s="2" t="inlineStr">
-        <is>
-          <t>140.5</t>
-        </is>
-      </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>15/30</t>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>7/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>8/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67057D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>148分钟</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±10分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>10/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,14 +2858,14 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5117,7 +5117,7 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
           <t>133.0</t>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7140,7 +7140,7 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8368,27 +8368,31 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：17:21采样，终点ETA 13分钟</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8396,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8420,12 +8424,12 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
@@ -8445,7 +8449,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>146.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8515,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8721,7 +8725,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8749,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8853,12 +8857,12 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
@@ -8880,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8929,7 +8933,7 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>142.3</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8972,24 +8976,24 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数51分钟，约±8分钟</t>
+          <t>17:31采样：该车到重点站周东路川周公路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±9分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -8999,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9048,12 +9052,12 @@
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>154.0</t>
+          <t>152.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9091,24 +9095,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站浦建路锦绣路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±12分钟</t>
+          <t>17:31采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9118,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9167,7 +9171,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>145.5</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9440,19 +9444,19 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站锦绣路花木路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
+          <t>17:31采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
@@ -9467,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9516,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>152.7</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9559,19 +9563,19 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:38</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站迎春路长柳路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数77分钟，约±12分钟</t>
+          <t>17:31采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
@@ -9586,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9635,12 +9639,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>134.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -9678,7 +9682,7 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -9690,7 +9694,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路高科西路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
@@ -9705,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9797,19 +9801,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:13</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站丁香路锦绣路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数91分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9824,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9873,7 +9877,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>152.3</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9916,19 +9920,19 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
+          <t>17:31采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
@@ -9943,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9992,12 +9996,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>133.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -10035,24 +10039,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站康沈路秀康路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数97分钟，约±12分钟</t>
+          <t>17:31采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±13分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10062,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10111,7 +10115,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.8</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10166,7 +10170,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站金杨路金业路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10181,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10285,12 +10289,12 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站康丽路康恩路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数145分钟，约±10分钟</t>
+          <t>17:31采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10300,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10324,7 +10328,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
@@ -10392,7 +10396,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -10404,7 +10408,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:21采样：该车到重点站莱阳路东陆路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±5分钟</t>
+          <t>17:31采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10419,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10534,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10588,7 +10592,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10818,7 +10822,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10998,7 +11002,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11056,6 +11060,121 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:31</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>3/30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC90"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2501,14 +2501,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>143.3</t>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2625,17 +2625,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3096,14 +3096,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>134.7</t>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3215,22 +3215,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3572,22 +3572,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4350,7 +4350,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5107,22 +5107,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,14 +5583,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>143.3</t>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,14 +6293,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>134.7</t>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6422,12 +6422,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7606,14 +7606,14 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
           <t>143.3</t>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,14 +7725,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>134.7</t>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8325,17 +8325,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8611,24 +8611,24 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>138分钟</t>
+          <t>139分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq50，推进22站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8857,24 +8857,24 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>139分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8923,22 +8923,22 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>142.0</t>
+          <t>141.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8971,29 +8971,29 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>149分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站周东路川周公路 ETA 22分钟；叠加该车自身同类时段从该站到终点历史中位数21分钟，约±9分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9027,12 +9027,12 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
@@ -9042,22 +9042,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>152.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9090,29 +9090,29 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>146分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9146,12 +9146,12 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
@@ -9161,22 +9161,22 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>144.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9295,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9439,29 +9439,29 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站锦绣路花木路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数73分钟，约±13分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9495,12 +9495,12 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>155.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9558,29 +9558,29 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站浦建路锦绣路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±12分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9614,12 +9614,12 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -9677,29 +9677,29 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>19:09</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>145分钟</t>
+          <t>159分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站沪南路高科西路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数81分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9733,12 +9733,12 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>144.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9801,19 +9801,19 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站白桦路明月路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数99分钟，约±5分钟</t>
+          <t>18:13采样：该车到重点站沪南路北中路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9920,24 +9920,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>144分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站沪南路华夏西路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±12分钟</t>
+          <t>18:13采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>133.7</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10039,24 +10039,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:08</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站沪南路华夏西路 ETA 12分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±13分钟</t>
+          <t>18:13采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10066,7 +10066,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10115,7 +10115,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10158,19 +10158,19 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:26</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>146分钟</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站金杨路金业路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数112分钟，约±5分钟</t>
+          <t>18:13采样：该车到重点站浦建路锦绣路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10234,12 +10234,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>141.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10277,19 +10277,19 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>157分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站川周公路康沈路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数130分钟，约±12分钟</t>
+          <t>18:13采样：该车到重点站沪南路高科西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±12分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>144.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10396,19 +10396,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>17:31采样：该车到重点站莱阳路东陆路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数139分钟，约±5分钟</t>
+          <t>18:13采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -10515,22 +10515,26 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>18:13采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10538,7 +10542,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,17 +10566,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10582,17 +10586,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10630,22 +10634,26 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>18:13采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10653,7 +10661,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10677,17 +10685,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10697,17 +10705,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>142.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -10745,22 +10753,26 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:34</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>18:13采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10768,7 +10780,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10792,17 +10804,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10812,17 +10824,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10895,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10937,7 +10949,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -10975,19 +10987,19 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>20:36</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数148分钟估算，约±10分钟</t>
+          <t>18:13采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±10分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
@@ -11002,7 +11014,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11031,7 +11043,7 @@
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
@@ -11056,7 +11068,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11117,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11171,7 +11183,586 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
+          <t>2/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>134.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
           <t>3/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>143.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>16/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>148.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>141.3</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>12/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>21:38</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>143分钟</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±9分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:13</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>144.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>18/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,12 +956,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2739,22 +2739,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3334,22 +3334,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3806,22 +3806,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,22 +5464,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,22 +5702,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,22 +6174,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6412,22 +6412,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>144.3</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9280,22 +9280,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>144.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -9444,24 +9444,24 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>160分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9510,22 +9510,22 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>155.3</t>
+          <t>148.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -9563,24 +9563,24 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9629,17 +9629,17 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>135.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9682,24 +9682,24 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>19:09</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>159分钟</t>
+          <t>152分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N78" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9748,22 +9748,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>144.7</t>
+          <t>142.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -9796,29 +9796,29 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>19:16</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>161分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站沪南路北中路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9852,12 +9852,12 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
@@ -9867,22 +9867,22 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>154.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -9915,29 +9915,29 @@
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±7分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9971,12 +9971,12 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
@@ -9986,22 +9986,22 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -10039,26 +10039,22 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>19:17</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站迎春路金松路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数59分钟，约±12分钟</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:20采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10066,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10090,12 +10086,12 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
@@ -10115,12 +10111,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -10153,29 +10149,29 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>156分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站浦建路锦绣路 ETA 16分钟；叠加该车自身同类时段从该站到终点历史中位数63分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10185,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10209,12 +10205,12 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
@@ -10234,12 +10230,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -10277,24 +10273,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>19:48</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>157分钟</t>
+          <t>148分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站沪南路高科西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数94分钟，约±12分钟</t>
+          <t>19:20采样：该车到重点站五莲路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10304,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10328,7 +10324,7 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
@@ -10353,12 +10349,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>144.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -10396,19 +10392,19 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:52</t>
+          <t>19:49</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>152分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站丁香路锦绣路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数93分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10423,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10462,22 +10458,22 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>136.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -10515,19 +10511,19 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>155分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站沪南路华夏西路 ETA 11分钟；叠加该车自身同类时段从该站到终点历史中位数102分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
@@ -10542,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10591,12 +10587,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10630,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>20:11</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -10646,7 +10642,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站金杨路金业路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数116分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -10661,7 +10657,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10715,7 +10711,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -10753,19 +10749,19 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>154分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站川周公路康沈路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数133分钟，约±5分钟</t>
+          <t>19:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -10780,7 +10776,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10829,12 +10825,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -10895,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10949,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -10987,24 +10983,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:36</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>147分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>18:13采样：该车到重点站康丽路康恩路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数143分钟，约±10分钟</t>
+          <t>19:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11014,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11063,12 +11059,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>8/30</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11183,7 +11179,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>1/30</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11336,22 +11332,26 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>19:20采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11383,17 +11383,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11403,17 +11403,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>143.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11528,7 +11528,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11589,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11643,7 +11643,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -11651,24 +11651,24 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -11681,34 +11681,30 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数143分钟估算，约±9分钟</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11722,47 +11718,868 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>142.3</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>14/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
           <t>19:15</t>
         </is>
       </c>
-      <c r="V95" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>21:46</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>151分钟</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>19:20采样：该车到重点站川周公路康沈路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W95" s="2" t="inlineStr">
+      <c r="W96" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X95" s="2" t="inlineStr">
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>22/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>130分钟</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y95" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z95" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>144.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>19/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68261D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA95" s="2" t="inlineStr">
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>137.7</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>6/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>21:47</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>148.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>24/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>144.3</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
-        <is>
-          <t>18/30</t>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>135.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>4/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A09172D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>证据不足</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>154.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>25/30</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>136.2</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>5/30</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC102"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2858,22 +2858,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       <c r="AB33" s="2" t="inlineStr"/>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4527,7 +4527,7 @@
       <c r="AB34" s="2" t="inlineStr"/>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -4592,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4755,17 +4755,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5187,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       <c r="AB55" s="2" t="inlineStr"/>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,12 +7497,12 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>18/31</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -8281,7 +8281,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8330,12 +8330,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8563,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8638,7 +8638,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8687,12 +8687,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
       <c r="AB70" s="2" t="inlineStr"/>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9406,7 +9406,7 @@
       <c r="AB75" s="2" t="inlineStr"/>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>—/30</t>
+          <t>—/31</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9644,7 +9644,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9872,17 +9872,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>149.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>25/31</t>
         </is>
       </c>
     </row>
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10154,24 +10154,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>19:36</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>156分钟</t>
+          <t>162分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10230,12 +10230,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>147.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -10273,26 +10273,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:48</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>148分钟</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站五莲路兰城路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：19:40采样，终点ETA 6分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10300,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10329,7 +10325,7 @@
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
@@ -10349,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>142.5</t>
+          <t>142.2</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -10387,24 +10383,24 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>19:49</t>
+          <t>19:43</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>150分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站周东路川周公路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数22分钟，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M84" s="2" t="inlineStr">
@@ -10419,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10443,12 +10439,12 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
@@ -10468,12 +10464,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>136.2</t>
+          <t>134.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -10506,29 +10502,29 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>155分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站云山路碧云路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数54分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10538,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,12 +10558,12 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
@@ -10587,12 +10583,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/31</t>
         </is>
       </c>
     </row>
@@ -10625,7 +10621,7 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -10635,19 +10631,19 @@
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站沪南路御桥路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数44分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr">
@@ -10657,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10681,12 +10677,12 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
@@ -10706,12 +10702,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -10744,29 +10740,29 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>154分钟</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10776,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10800,12 +10796,12 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
@@ -10825,12 +10821,12 @@
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>137.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>7/31</t>
         </is>
       </c>
     </row>
@@ -10863,27 +10859,31 @@
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>150分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10915,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10935,17 +10935,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>141.0</t>
+          <t>143.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10983,24 +10983,24 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
+          <t>19:31采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N89" s="2" t="inlineStr">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.0</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>8/30</t>
+          <t>9/31</t>
         </is>
       </c>
     </row>
@@ -11102,19 +11102,19 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr"/>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,37 +11149,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>1/30</t>
+          <t>2/31</t>
         </is>
       </c>
     </row>
@@ -11212,27 +11212,31 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:47</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>142分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -11240,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11268,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,17 +11288,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>134.7</t>
+          <t>136.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11332,19 +11336,19 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站白桦路明月路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数85分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M92" s="2" t="inlineStr">
@@ -11359,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11408,12 +11412,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>139.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11528,7 +11532,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -11589,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11643,7 +11647,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11704,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11758,7 +11762,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -11796,19 +11800,19 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>151分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>19:20采样：该车到重点站川周公路康沈路 ETA 13分钟；叠加该车自身同类时段从该站到终点历史中位数132分钟，约±5分钟</t>
+          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
@@ -11823,7 +11827,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11872,12 +11876,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -11915,19 +11919,19 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:27</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数130分钟估算，约±5分钟</t>
+          <t>20:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
@@ -11942,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11971,7 +11975,7 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11991,12 +11995,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>144.0</t>
+          <t>143.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12111,7 +12115,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -12149,24 +12153,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±6分钟</t>
+          <t>20:20采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12176,7 +12180,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12205,7 +12209,7 @@
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12225,12 +12229,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>150.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>26/31</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12295,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12345,7 +12349,7 @@
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -12353,24 +12357,24 @@
       <c r="A101" s="2" t="inlineStr"/>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>20:05</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -12383,30 +12387,34 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>20:20采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12420,7 +12428,7 @@
       <c r="T101" s="2" t="inlineStr"/>
       <c r="U101" s="2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="V101" s="2" t="inlineStr">
@@ -12430,37 +12438,37 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>154.7</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>1/31</t>
         </is>
       </c>
     </row>
@@ -12468,7 +12476,7 @@
       <c r="A102" s="2" t="inlineStr"/>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -12478,7 +12486,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -12498,34 +12506,34 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:16</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±7分钟</t>
+          <t>20:20采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12539,47 +12547,285 @@
       <c r="T102" s="2" t="inlineStr"/>
       <c r="U102" s="2" t="inlineStr">
         <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>同车重点站剩余时间</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>25/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
           <t>20:30</t>
         </is>
       </c>
-      <c r="V102" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>22:37</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>127分钟</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±7分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W102" s="2" t="inlineStr">
+      <c r="W103" s="2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="X102" s="2" t="inlineStr">
+      <c r="X103" s="2" t="inlineStr">
         <is>
           <t>同车历史全程时间</t>
         </is>
       </c>
-      <c r="Y102" s="2" t="inlineStr">
+      <c r="Y103" s="2" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="Z102" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AA102" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB102" s="2" t="inlineStr">
-        <is>
-          <t>136.2</t>
-        </is>
-      </c>
-      <c r="AC102" s="2" t="inlineStr">
-        <is>
-          <t>5/30</t>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>134.5</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>3/31</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>125分钟</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>同车历史全程时间</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>2/31</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4884,7 +4884,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -5068,7 +5068,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5112,17 +5112,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -6899,7 +6899,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>18/31</t>
+          <t>20/31</t>
         </is>
       </c>
     </row>
@@ -7978,7 +7978,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/31</t>
+          <t>15/31</t>
         </is>
       </c>
     </row>
@@ -8335,7 +8335,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>22/31</t>
+          <t>23/31</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -8692,7 +8692,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8928,17 +8928,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -9003,7 +9003,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9047,17 +9047,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9171,12 +9171,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -9356,7 +9356,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9634,17 +9634,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9709,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9763,7 +9763,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>23/31</t>
+          <t>24/31</t>
         </is>
       </c>
     </row>
@@ -10350,7 +10350,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>14/31</t>
+          <t>16/31</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10464,12 +10464,12 @@
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>17/31</t>
+          <t>19/31</t>
         </is>
       </c>
     </row>
@@ -10945,7 +10945,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>19/31</t>
+          <t>21/31</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/31</t>
+          <t>10/31</t>
         </is>
       </c>
     </row>
@@ -11097,12 +11097,12 @@
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -11114,10 +11114,14 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:20采样，终点ETA 12分钟</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -11125,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11149,12 +11153,12 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
@@ -11174,7 +11178,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11217,12 +11221,12 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:47</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>142分钟</t>
+          <t>143分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
@@ -11244,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11293,7 +11297,7 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>136.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11336,26 +11340,22 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站康沈路秀沿路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数25分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：20:40采样，终点ETA 9分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>139.2</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/31</t>
+          <t>13/31</t>
         </is>
       </c>
     </row>
@@ -11455,19 +11455,19 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：20:31采样，终点ETA 26分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr"/>
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11502,17 +11502,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11522,17 +11522,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>24/31</t>
+          <t>14/31</t>
         </is>
       </c>
     </row>
@@ -11565,27 +11565,31 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11593,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11617,17 +11621,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11637,17 +11641,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>141.3</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/31</t>
+          <t>12/31</t>
         </is>
       </c>
     </row>
@@ -11675,12 +11679,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11708,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11716,10 +11720,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>丁香路锦绣路</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq29映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11737,7 +11757,7 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
@@ -11762,7 +11782,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>15/31</t>
+          <t>17/31</t>
         </is>
       </c>
     </row>
@@ -11795,29 +11815,29 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>141分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路金松路 ETA 1分钟；叠加该车自身同类时段从该站到终点历史中位数74分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11827,7 +11847,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11851,12 +11871,12 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
@@ -11876,12 +11896,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>143.7</t>
+          <t>137.7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>21/31</t>
+          <t>8/31</t>
         </is>
       </c>
     </row>
@@ -11914,29 +11934,29 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站迎春路长柳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数65分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11946,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11970,12 +11990,12 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
@@ -11995,12 +12015,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>143.5</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>20/31</t>
+          <t>22/31</t>
         </is>
       </c>
     </row>
@@ -12028,12 +12048,12 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12061,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12069,10 +12089,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr"/>
-      <c r="R98" s="2" t="inlineStr"/>
-      <c r="S98" s="2" t="inlineStr"/>
-      <c r="T98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="inlineStr">
+        <is>
+          <t>20:27</t>
+        </is>
+      </c>
+      <c r="T98" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 1分钟参与校验</t>
+        </is>
+      </c>
       <c r="U98" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -12090,7 +12126,7 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
@@ -12158,21 +12194,17 @@
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站金杨路云山路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数87分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 31分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12180,7 +12212,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12204,12 +12236,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12229,7 +12261,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>149.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12272,19 +12304,19 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:44</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 23分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr"/>
@@ -12295,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12351,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12339,17 +12371,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>135.7</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12387,24 +12419,24 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站博兴路兰城路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数106分钟，约±7分钟</t>
+          <t>21:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12414,7 +12446,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12463,7 +12495,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>121.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12511,14 +12543,14 @@
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>20:20采样：该车到重点站川周公路康沈路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数113分钟，约±5分钟</t>
+          <t>21:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M102" s="2" t="inlineStr">
@@ -12533,7 +12565,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12582,7 +12614,7 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>149.0</t>
+          <t>148.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12625,19 +12657,19 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:34</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数127分钟估算，约±7分钟</t>
+          <t>21:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
@@ -12652,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12681,7 +12713,7 @@
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
@@ -12701,12 +12733,12 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>134.5</t>
+          <t>133.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>3/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -12749,14 +12781,14 @@
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>125分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数125分钟估算，约±5分钟</t>
+          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -12771,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12800,7 +12832,7 @@
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
@@ -12820,7 +12852,7 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>131.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="22" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -5306,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5950,7 +5950,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -9241,7 +9241,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9947,7 +9947,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>4/31</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10459,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -11939,24 +11939,24 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>21:34</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N97" s="2" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>145.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq63，推进35站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12184,27 +12184,31 @@
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>21:52</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 31分钟</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -12212,7 +12216,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12236,12 +12240,12 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
@@ -12261,7 +12265,7 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>149.8</t>
+          <t>149.2</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12299,7 +12303,7 @@
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
@@ -12316,10 +12320,14 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 23分钟</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12327,7 +12335,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12351,12 +12359,12 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
@@ -12414,29 +12422,29 @@
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>21:59</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>119分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站沪南路御桥路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±6分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N101" s="2" t="inlineStr">
@@ -12446,7 +12454,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12470,12 +12478,12 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
@@ -12495,7 +12503,7 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>121.0</t>
+          <t>119.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12538,26 +12546,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>22:16</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站锦绣路罗山路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数55分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 21分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12565,7 +12569,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12589,12 +12593,12 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
@@ -12614,7 +12618,7 @@
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>148.8</t>
+          <t>147.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
@@ -12657,26 +12661,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:34</t>
+          <t>22:37</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站锦绣路花木路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数67分钟，约±7分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 47分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12728,17 +12728,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>133.8</t>
+          <t>137.0</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -12776,19 +12776,19 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:52</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站沪南路华夏西路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
@@ -12803,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>131.2</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">

--- a/data/export/2026-09-18-浦东35路.xlsx
+++ b/data/export/2026-09-18-浦东35路.xlsx
@@ -453,7 +453,7 @@
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="22" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
     <col width="14" customWidth="1" min="25" max="25"/>
     <col width="18" customWidth="1" min="26" max="26"/>
     <col width="18" customWidth="1" min="27" max="27"/>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/31</t>
+          <t>5/31</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10459,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11302,7 +11302,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/31</t>
+          <t>6/31</t>
         </is>
       </c>
     </row>
@@ -12656,27 +12656,31 @@
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>22:37</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:50采样，终点ETA 47分钟</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12684,7 +12688,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12708,17 +12712,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底（误差可能&gt;15分钟）</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12728,17 +12732,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>137.0</t>
+          <t>132.8</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>6/31</t>
+          <t>3/31</t>
         </is>
       </c>
     </row>
@@ -12788,14 +12792,10 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数58分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：22:29采样，终点ETA 23分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:50</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12827,12 +12827,12 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
